--- a/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.8571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9281</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.25</v>
+        <v>0.5667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.5833</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9302</v>
+        <v>0.9651</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8673</v>
+        <v>0.8247</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1009,136 +1009,478 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8603</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: Increasing the security of the system by reducing the gateways to the outside, as the only way to interact with the microservices is through the Api Gateway.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>C_05, Security</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_06, P_03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
+          <t>*CF_M01_C07</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.928</v>
+        <v>0.8413</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C_01, C_02, C_03, C_04</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>P_01, P_02</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9373</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.5</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>It is only the Api Gateway that is responsible for authorization and SSL with the client.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C_05, Security</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AU_06</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>*CF_M01_C07</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>43</v>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>For the data transmission to be as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real time.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C_01, Performance</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD05</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>The use of this language was decided, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9898</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8603</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>The use of AWS was decided and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C_03, C_04</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,106 +1537,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>The Amazon S3 service is a necessary service to be able to develop a data lake, since this service allows us to store any element that is needed.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>C_03, C_04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_12, AU_16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6949</v>
+        <v>0.6754</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module.</t>
+          <t>This service, being a serverless service, means that it is not necessary to manage the infrastructure when there is an increase in the set of data and users.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_24, R_25, C_03, C_04</t>
+          <t>C_01, Scalability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_12, AU_16, AU_18, AU_19, AU_20, AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6404</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>S’ha decidit la utilització d’aquest llenguatge, i no JavaScript, ja que és el llenguatge per defecte per NestJS i perquè gràcies al seu tipatge estàtic permet la detecció d’errors en temps de compilació.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NestJS, TypeScript</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_13, AU_14</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5923</v>
+        <v>0.6661</v>
       </c>
     </row>
   </sheetData>
@@ -1308,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1351,67 +1658,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6404</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M01_AD03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gives the ability to handle partial system crashes</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M01_C08</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.5784</v>
+        <v>0.6364</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>0.2222</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8571</v>
+        <v>0.2857</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9281</v>
+        <v>0.8447</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5667</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5833</v>
+        <v>0.4167</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9651</v>
+        <v>0.9302</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.75</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -792,31 +792,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,7 +974,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8247</v>
+        <v>0.822</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1019,12 +1019,15 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: Increasing the security of the system by reducing the gateways to the outside, as the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway [27]. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma. L’ús d’aquest patró proveeix diversos avantatges al sistema, com poden ser:
+● Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.
+● Dona la capacitat de manegar caigudes parcials del sistema, manegant quins serveis estan en funcionament en tot moment.
+● Éssolament l’Api Gateway que s’encarreguen de l’autorització i el SSL amb el client.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>C_05, Increase system security, Handle partial system failures, Authorization and SSL with the client</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1059,28 +1062,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8413</v>
+        <v>0.8673</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1088,398 +1091,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3333</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8603</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C_01, C_02, C_03, C_04</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>P_01, P_02</t>
+          <t>AU_15, Low price, Previous use by the company</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M01_AD06</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9373</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M01_AD07</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9871</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>For the data transmission to be as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real time.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>C_01, Performance</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>CF_M01_C01</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M01_AD05</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>The use of this language was decided, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CF_M01_AU34</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9898</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8603</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>The use of AWS was decided and not other cloud services due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>C_03, C_04</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1494,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,71 +1198,246 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Amazon S3 service is a necessary service to be able to develop a data lake, since this service allows us to store any element that is needed.</t>
+          <t>Com a framework es farà ús de NestJS [2], amb el llenguatge Typescript [3], i per la infraestructura es farà ús dels serveis cloud d’AWS [4]. Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_12, AU_16</t>
+          <t>AU_13, AU_14, P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6754</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor. En aquest tipus d’arquitectura el client és qui realitza les peticions a un servidor, que les processa i retorna la resposta al client. En el nostre cas, el client és l’usuari de la plataforma i el servidor és el software que s’encarrega de processar les peticions de l’usuari.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_01, AU_02, P_01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP [26] i el model de REST API.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_23, P_01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6841</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_03, AU_04, AU_05, P_02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6347</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_02, C_03, C_04, C_05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_03, AU_04, AU_05, AU_06, AU_07, AU_08, AU_11, AU_12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>AD_07</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>This service, being a serverless service, means that it is not necessary to manage the infrastructure when there is an increase in the set of data and users.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C_01, Scalability</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Com es pot observar en la figura 9.1 la comunicació entre el servei de l’Api Gateway és mitjançant el protocol de comunicació TCP [29].</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_06, AU_07, AU_08, AU_09, AU_10, AU_24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>CF_M01_AD02</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0.6661</v>
+      <c r="G7" t="n">
+        <v>0.6289</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aquesta base de dades està implementada en el servei RDS [30], que és un servei de base de dades relacional distribuït d’AWS.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AU_11, AU_15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.627</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,34 +1494,164 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M01_AD03</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M01_C08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6258</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>AD_01</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.6364</v>
+      <c r="G4" t="n">
+        <v>0.6511</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6481</v>
       </c>
     </row>
   </sheetData>
